--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -230,7 +230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -375,6 +375,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -8525,26 +8546,32 @@
       <c r="H230" s="53" t="n"/>
     </row>
     <row r="231" ht="19.5" customHeight="1">
-      <c r="A231" s="10" t="n"/>
-      <c r="B231" s="27" t="n"/>
-      <c r="C231" s="34" t="n"/>
-      <c r="D231" s="11">
-        <f>IF(C231="","",C231*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E231" s="12">
-        <f>IF(C231="","",C231-D231)</f>
-        <v/>
-      </c>
-      <c r="F231" s="19">
-        <f>IF(OR(B231="",C231=""),"",E231-B231)</f>
-        <v/>
-      </c>
-      <c r="G231" s="22">
-        <f>IF(OR(B231="",B231=0),"",F231/B231)</f>
-        <v/>
-      </c>
-      <c r="H231" s="13" t="n"/>
+      <c r="A231" s="45" t="inlineStr">
+        <is>
+          <t>MAG-7 | Sand Dune .152819916606</t>
+        </is>
+      </c>
+      <c r="B231" s="54" t="n"/>
+      <c r="C231" s="55" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D231" s="56">
+        <f>C231*$B$1</f>
+        <v/>
+      </c>
+      <c r="E231" s="57">
+        <f>C231-D231</f>
+        <v/>
+      </c>
+      <c r="F231" s="58">
+        <f>E231-B231</f>
+        <v/>
+      </c>
+      <c r="G231" s="59">
+        <f>F231/B231</f>
+        <v/>
+      </c>
+      <c r="H231" s="60" t="n"/>
     </row>
     <row r="232" ht="19.5" customHeight="1">
       <c r="A232" s="6" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -8574,48 +8574,60 @@
       <c r="H231" s="60" t="n"/>
     </row>
     <row r="232" ht="19.5" customHeight="1">
-      <c r="A232" s="6" t="n"/>
-      <c r="B232" s="26" t="n"/>
-      <c r="C232" s="33" t="n"/>
-      <c r="D232" s="7">
-        <f>IF(C232="","",C232*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E232" s="8">
-        <f>IF(C232="","",C232-D232)</f>
-        <v/>
-      </c>
-      <c r="F232" s="18">
-        <f>IF(OR(B232="",C232=""),"",E232-B232)</f>
-        <v/>
-      </c>
-      <c r="G232" s="21">
-        <f>IF(OR(B232="",B232=0),"",F232/B232)</f>
-        <v/>
-      </c>
-      <c r="H232" s="9" t="n"/>
+      <c r="A232" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M249 | Contrast Spray 0.207938030362 Kenny Gold krakow </t>
+        </is>
+      </c>
+      <c r="B232" s="47" t="n"/>
+      <c r="C232" s="48" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="D232" s="49">
+        <f>C232*$B$1</f>
+        <v/>
+      </c>
+      <c r="E232" s="50">
+        <f>C232-D232</f>
+        <v/>
+      </c>
+      <c r="F232" s="51">
+        <f>E232-B232</f>
+        <v/>
+      </c>
+      <c r="G232" s="52">
+        <f>F232/B232</f>
+        <v/>
+      </c>
+      <c r="H232" s="53" t="n"/>
     </row>
     <row r="233" ht="19.5" customHeight="1">
-      <c r="A233" s="10" t="n"/>
-      <c r="B233" s="27" t="n"/>
-      <c r="C233" s="34" t="n"/>
-      <c r="D233" s="11">
-        <f>IF(C233="","",C233*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E233" s="12">
-        <f>IF(C233="","",C233-D233)</f>
-        <v/>
-      </c>
-      <c r="F233" s="19">
-        <f>IF(OR(B233="",C233=""),"",E233-B233)</f>
-        <v/>
-      </c>
-      <c r="G233" s="22">
-        <f>IF(OR(B233="",B233=0),"",F233/B233)</f>
-        <v/>
-      </c>
-      <c r="H233" s="13" t="n"/>
+      <c r="A233" s="45" t="inlineStr">
+        <is>
+          <t>Five-SeveN | Contractor 0.189471766353</t>
+        </is>
+      </c>
+      <c r="B233" s="54" t="n"/>
+      <c r="C233" s="55" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D233" s="56">
+        <f>C233*$B$1</f>
+        <v/>
+      </c>
+      <c r="E233" s="57">
+        <f>C233-D233</f>
+        <v/>
+      </c>
+      <c r="F233" s="58">
+        <f>E233-B233</f>
+        <v/>
+      </c>
+      <c r="G233" s="59">
+        <f>F233/B233</f>
+        <v/>
+      </c>
+      <c r="H233" s="60" t="n"/>
     </row>
     <row r="234" ht="19.5" customHeight="1">
       <c r="A234" s="6" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -8630,26 +8630,32 @@
       <c r="H233" s="60" t="n"/>
     </row>
     <row r="234" ht="19.5" customHeight="1">
-      <c r="A234" s="6" t="n"/>
-      <c r="B234" s="26" t="n"/>
-      <c r="C234" s="33" t="n"/>
-      <c r="D234" s="7">
-        <f>IF(C234="","",C234*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E234" s="8">
-        <f>IF(C234="","",C234-D234)</f>
-        <v/>
-      </c>
-      <c r="F234" s="18">
-        <f>IF(OR(B234="",C234=""),"",E234-B234)</f>
-        <v/>
-      </c>
-      <c r="G234" s="21">
-        <f>IF(OR(B234="",B234=0),"",F234/B234)</f>
-        <v/>
-      </c>
-      <c r="H234" s="9" t="n"/>
+      <c r="A234" s="46" t="inlineStr">
+        <is>
+          <t>MP9 | Sand Dashed 0.746735513210</t>
+        </is>
+      </c>
+      <c r="B234" s="47" t="n"/>
+      <c r="C234" s="48" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D234" s="49">
+        <f>C234*$B$1</f>
+        <v/>
+      </c>
+      <c r="E234" s="50">
+        <f>C234-D234</f>
+        <v/>
+      </c>
+      <c r="F234" s="51">
+        <f>E234-B234</f>
+        <v/>
+      </c>
+      <c r="G234" s="52">
+        <f>F234/B234</f>
+        <v/>
+      </c>
+      <c r="H234" s="53" t="n"/>
     </row>
     <row r="235" ht="19.5" customHeight="1">
       <c r="A235" s="10" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -8658,26 +8658,32 @@
       <c r="H234" s="53" t="n"/>
     </row>
     <row r="235" ht="19.5" customHeight="1">
-      <c r="A235" s="10" t="n"/>
-      <c r="B235" s="27" t="n"/>
-      <c r="C235" s="34" t="n"/>
-      <c r="D235" s="11">
-        <f>IF(C235="","",C235*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E235" s="12">
-        <f>IF(C235="","",C235-D235)</f>
-        <v/>
-      </c>
-      <c r="F235" s="19">
-        <f>IF(OR(B235="",C235=""),"",E235-B235)</f>
-        <v/>
-      </c>
-      <c r="G235" s="22">
-        <f>IF(OR(B235="",B235=0),"",F235/B235)</f>
-        <v/>
-      </c>
-      <c r="H235" s="13" t="n"/>
+      <c r="A235" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Awp Assimove crown foil </t>
+        </is>
+      </c>
+      <c r="B235" s="54" t="n"/>
+      <c r="C235" s="55" t="n">
+        <v>195</v>
+      </c>
+      <c r="D235" s="56">
+        <f>C235*$B$1</f>
+        <v/>
+      </c>
+      <c r="E235" s="57">
+        <f>C235-D235</f>
+        <v/>
+      </c>
+      <c r="F235" s="58">
+        <f>E235-B235</f>
+        <v/>
+      </c>
+      <c r="G235" s="59">
+        <f>F235/B235</f>
+        <v/>
+      </c>
+      <c r="H235" s="60" t="n"/>
     </row>
     <row r="236" ht="19.5" customHeight="1">
       <c r="A236" s="6" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -8686,26 +8686,32 @@
       <c r="H235" s="60" t="n"/>
     </row>
     <row r="236" ht="19.5" customHeight="1">
-      <c r="A236" s="6" t="n"/>
-      <c r="B236" s="26" t="n"/>
-      <c r="C236" s="33" t="n"/>
-      <c r="D236" s="7">
-        <f>IF(C236="","",C236*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E236" s="8">
-        <f>IF(C236="","",C236-D236)</f>
-        <v/>
-      </c>
-      <c r="F236" s="18">
-        <f>IF(OR(B236="",C236=""),"",E236-B236)</f>
-        <v/>
-      </c>
-      <c r="G236" s="21">
-        <f>IF(OR(B236="",B236=0),"",F236/B236)</f>
-        <v/>
-      </c>
-      <c r="H236" s="9" t="n"/>
+      <c r="A236" s="46" t="inlineStr">
+        <is>
+          <t>MAG-7 | Storm 0.297249525785 Device Gold Krakow</t>
+        </is>
+      </c>
+      <c r="B236" s="47" t="n"/>
+      <c r="C236" s="48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D236" s="49">
+        <f>C236*$B$1</f>
+        <v/>
+      </c>
+      <c r="E236" s="50">
+        <f>C236-D236</f>
+        <v/>
+      </c>
+      <c r="F236" s="51">
+        <f>E236-B236</f>
+        <v/>
+      </c>
+      <c r="G236" s="52">
+        <f>F236/B236</f>
+        <v/>
+      </c>
+      <c r="H236" s="53" t="n"/>
     </row>
     <row r="237" ht="19.5" customHeight="1">
       <c r="A237" s="10" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -8714,26 +8714,32 @@
       <c r="H236" s="53" t="n"/>
     </row>
     <row r="237" ht="19.5" customHeight="1">
-      <c r="A237" s="10" t="n"/>
-      <c r="B237" s="27" t="n"/>
-      <c r="C237" s="34" t="n"/>
-      <c r="D237" s="11">
-        <f>IF(C237="","",C237*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E237" s="12">
-        <f>IF(C237="","",C237-D237)</f>
-        <v/>
-      </c>
-      <c r="F237" s="19">
-        <f>IF(OR(B237="",C237=""),"",E237-B237)</f>
-        <v/>
-      </c>
-      <c r="G237" s="22">
-        <f>IF(OR(B237="",B237=0),"",F237/B237)</f>
-        <v/>
-      </c>
-      <c r="H237" s="13" t="n"/>
+      <c r="A237" s="45" t="inlineStr">
+        <is>
+          <t>USP-S | Royal Blue 0.383412957191</t>
+        </is>
+      </c>
+      <c r="B237" s="54" t="n"/>
+      <c r="C237" s="55" t="n">
+        <v>16</v>
+      </c>
+      <c r="D237" s="56">
+        <f>C237*$B$1</f>
+        <v/>
+      </c>
+      <c r="E237" s="57">
+        <f>C237-D237</f>
+        <v/>
+      </c>
+      <c r="F237" s="58">
+        <f>E237-B237</f>
+        <v/>
+      </c>
+      <c r="G237" s="59">
+        <f>F237/B237</f>
+        <v/>
+      </c>
+      <c r="H237" s="60" t="n"/>
     </row>
     <row r="238" ht="19.5" customHeight="1">
       <c r="A238" s="6" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -8742,70 +8742,88 @@
       <c r="H237" s="60" t="n"/>
     </row>
     <row r="238" ht="19.5" customHeight="1">
-      <c r="A238" s="6" t="n"/>
-      <c r="B238" s="26" t="n"/>
-      <c r="C238" s="33" t="n"/>
-      <c r="D238" s="7">
-        <f>IF(C238="","",C238*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E238" s="8">
-        <f>IF(C238="","",C238-D238)</f>
-        <v/>
-      </c>
-      <c r="F238" s="18">
-        <f>IF(OR(B238="",C238=""),"",E238-B238)</f>
-        <v/>
-      </c>
-      <c r="G238" s="21">
-        <f>IF(OR(B238="",B238=0),"",F238/B238)</f>
-        <v/>
-      </c>
-      <c r="H238" s="9" t="n"/>
+      <c r="A238" s="46" t="inlineStr">
+        <is>
+          <t>SG 553 | Fallout Warning 0.300346434116 Kato 2015 gold</t>
+        </is>
+      </c>
+      <c r="B238" s="47" t="n"/>
+      <c r="C238" s="48" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D238" s="49">
+        <f>C238*$B$1</f>
+        <v/>
+      </c>
+      <c r="E238" s="50">
+        <f>C238-D238</f>
+        <v/>
+      </c>
+      <c r="F238" s="51">
+        <f>E238-B238</f>
+        <v/>
+      </c>
+      <c r="G238" s="52">
+        <f>F238/B238</f>
+        <v/>
+      </c>
+      <c r="H238" s="53" t="n"/>
     </row>
     <row r="239" ht="19.5" customHeight="1">
-      <c r="A239" s="10" t="n"/>
-      <c r="B239" s="27" t="n"/>
-      <c r="C239" s="34" t="n"/>
-      <c r="D239" s="11">
-        <f>IF(C239="","",C239*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E239" s="12">
-        <f>IF(C239="","",C239-D239)</f>
-        <v/>
-      </c>
-      <c r="F239" s="19">
-        <f>IF(OR(B239="",C239=""),"",E239-B239)</f>
-        <v/>
-      </c>
-      <c r="G239" s="22">
-        <f>IF(OR(B239="",B239=0),"",F239/B239)</f>
-        <v/>
-      </c>
-      <c r="H239" s="13" t="n"/>
+      <c r="A239" s="45" t="inlineStr">
+        <is>
+          <t>G3SG1 | Desert Storm 0.797657728195</t>
+        </is>
+      </c>
+      <c r="B239" s="54" t="n"/>
+      <c r="C239" s="55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D239" s="56">
+        <f>C239*$B$1</f>
+        <v/>
+      </c>
+      <c r="E239" s="57">
+        <f>C239-D239</f>
+        <v/>
+      </c>
+      <c r="F239" s="58">
+        <f>E239-B239</f>
+        <v/>
+      </c>
+      <c r="G239" s="59">
+        <f>F239/B239</f>
+        <v/>
+      </c>
+      <c r="H239" s="60" t="n"/>
     </row>
     <row r="240" ht="19.5" customHeight="1">
-      <c r="A240" s="6" t="n"/>
-      <c r="B240" s="26" t="n"/>
-      <c r="C240" s="33" t="n"/>
-      <c r="D240" s="7">
-        <f>IF(C240="","",C240*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E240" s="8">
-        <f>IF(C240="","",C240-D240)</f>
-        <v/>
-      </c>
-      <c r="F240" s="18">
-        <f>IF(OR(B240="",C240=""),"",E240-B240)</f>
-        <v/>
-      </c>
-      <c r="G240" s="21">
-        <f>IF(OR(B240="",B240=0),"",F240/B240)</f>
-        <v/>
-      </c>
-      <c r="H240" s="9" t="n"/>
+      <c r="A240" s="46" t="inlineStr">
+        <is>
+          <t>Nova | Polar Mesh 0.217678815126</t>
+        </is>
+      </c>
+      <c r="B240" s="47" t="n"/>
+      <c r="C240" s="48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D240" s="49">
+        <f>C240*$B$1</f>
+        <v/>
+      </c>
+      <c r="E240" s="50">
+        <f>C240-D240</f>
+        <v/>
+      </c>
+      <c r="F240" s="51">
+        <f>E240-B240</f>
+        <v/>
+      </c>
+      <c r="G240" s="52">
+        <f>F240/B240</f>
+        <v/>
+      </c>
+      <c r="H240" s="53" t="n"/>
     </row>
     <row r="241" ht="19.5" customHeight="1">
       <c r="A241" s="10" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -8826,48 +8826,60 @@
       <c r="H240" s="53" t="n"/>
     </row>
     <row r="241" ht="19.5" customHeight="1">
-      <c r="A241" s="10" t="n"/>
-      <c r="B241" s="27" t="n"/>
-      <c r="C241" s="34" t="n"/>
-      <c r="D241" s="11">
-        <f>IF(C241="","",C241*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E241" s="12">
-        <f>IF(C241="","",C241-D241)</f>
-        <v/>
-      </c>
-      <c r="F241" s="19">
-        <f>IF(OR(B241="",C241=""),"",E241-B241)</f>
-        <v/>
-      </c>
-      <c r="G241" s="22">
-        <f>IF(OR(B241="",B241=0),"",F241/B241)</f>
-        <v/>
-      </c>
-      <c r="H241" s="13" t="n"/>
+      <c r="A241" s="45" t="inlineStr">
+        <is>
+          <t>Sawed-Off | Irradiated Alert 3dMax kato gold (not full set) 0.392642</t>
+        </is>
+      </c>
+      <c r="B241" s="54" t="n"/>
+      <c r="C241" s="55" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D241" s="56">
+        <f>C241*$B$1</f>
+        <v/>
+      </c>
+      <c r="E241" s="57">
+        <f>C241-D241</f>
+        <v/>
+      </c>
+      <c r="F241" s="58">
+        <f>E241-B241</f>
+        <v/>
+      </c>
+      <c r="G241" s="59">
+        <f>F241/B241</f>
+        <v/>
+      </c>
+      <c r="H241" s="60" t="n"/>
     </row>
     <row r="242" ht="19.5" customHeight="1">
-      <c r="A242" s="6" t="n"/>
-      <c r="B242" s="26" t="n"/>
-      <c r="C242" s="33" t="n"/>
-      <c r="D242" s="7">
-        <f>IF(C242="","",C242*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E242" s="8">
-        <f>IF(C242="","",C242-D242)</f>
-        <v/>
-      </c>
-      <c r="F242" s="18">
-        <f>IF(OR(B242="",C242=""),"",E242-B242)</f>
-        <v/>
-      </c>
-      <c r="G242" s="21">
-        <f>IF(OR(B242="",B242=0),"",F242/B242)</f>
-        <v/>
-      </c>
-      <c r="H242" s="9" t="n"/>
+      <c r="A242" s="46" t="inlineStr">
+        <is>
+          <t>0.0.384038507938 Nova walnut kato2015</t>
+        </is>
+      </c>
+      <c r="B242" s="47" t="n"/>
+      <c r="C242" s="48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D242" s="49">
+        <f>C242*$B$1</f>
+        <v/>
+      </c>
+      <c r="E242" s="50">
+        <f>C242-D242</f>
+        <v/>
+      </c>
+      <c r="F242" s="51">
+        <f>E242-B242</f>
+        <v/>
+      </c>
+      <c r="G242" s="52">
+        <f>F242/B242</f>
+        <v/>
+      </c>
+      <c r="H242" s="53" t="n"/>
     </row>
     <row r="243" ht="19.5" customHeight="1">
       <c r="A243" s="10" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -8882,26 +8882,34 @@
       <c r="H242" s="53" t="n"/>
     </row>
     <row r="243" ht="19.5" customHeight="1">
-      <c r="A243" s="10" t="n"/>
-      <c r="B243" s="27" t="n"/>
-      <c r="C243" s="34" t="n"/>
-      <c r="D243" s="11">
-        <f>IF(C243="","",C243*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E243" s="12">
-        <f>IF(C243="","",C243-D243)</f>
-        <v/>
-      </c>
-      <c r="F243" s="19">
-        <f>IF(OR(B243="",C243=""),"",E243-B243)</f>
-        <v/>
-      </c>
-      <c r="G243" s="22">
-        <f>IF(OR(B243="",B243=0),"",F243/B243)</f>
-        <v/>
-      </c>
-      <c r="H243" s="13" t="n"/>
+      <c r="A243" s="45" t="inlineStr">
+        <is>
+          <t>MP9 | Sand Dashed 0.241834059358</t>
+        </is>
+      </c>
+      <c r="B243" s="54" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C243" s="55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D243" s="56">
+        <f>C243*$B$1</f>
+        <v/>
+      </c>
+      <c r="E243" s="57">
+        <f>C243-D243</f>
+        <v/>
+      </c>
+      <c r="F243" s="58">
+        <f>E243-B243</f>
+        <v/>
+      </c>
+      <c r="G243" s="59">
+        <f>F243/B243</f>
+        <v/>
+      </c>
+      <c r="H243" s="60" t="n"/>
     </row>
     <row r="244" ht="19.5" customHeight="1">
       <c r="A244" s="6" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -8912,26 +8912,32 @@
       <c r="H243" s="60" t="n"/>
     </row>
     <row r="244" ht="19.5" customHeight="1">
-      <c r="A244" s="6" t="n"/>
-      <c r="B244" s="26" t="n"/>
-      <c r="C244" s="33" t="n"/>
-      <c r="D244" s="7">
-        <f>IF(C244="","",C244*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E244" s="8">
-        <f>IF(C244="","",C244-D244)</f>
-        <v/>
-      </c>
-      <c r="F244" s="18">
-        <f>IF(OR(B244="",C244=""),"",E244-B244)</f>
-        <v/>
-      </c>
-      <c r="G244" s="21">
-        <f>IF(OR(B244="",B244=0),"",F244/B244)</f>
-        <v/>
-      </c>
-      <c r="H244" s="9" t="n"/>
+      <c r="A244" s="46" t="inlineStr">
+        <is>
+          <t>SSG 08 Detour Atanta 0.172781</t>
+        </is>
+      </c>
+      <c r="B244" s="47" t="n"/>
+      <c r="C244" s="48" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="D244" s="49">
+        <f>C244*$B$1</f>
+        <v/>
+      </c>
+      <c r="E244" s="50">
+        <f>C244-D244</f>
+        <v/>
+      </c>
+      <c r="F244" s="51">
+        <f>E244-B244</f>
+        <v/>
+      </c>
+      <c r="G244" s="52">
+        <f>F244/B244</f>
+        <v/>
+      </c>
+      <c r="H244" s="53" t="n"/>
     </row>
     <row r="245" ht="19.5" customHeight="1">
       <c r="A245" s="10" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -8940,26 +8940,32 @@
       <c r="H244" s="53" t="n"/>
     </row>
     <row r="245" ht="19.5" customHeight="1">
-      <c r="A245" s="10" t="n"/>
-      <c r="B245" s="27" t="n"/>
-      <c r="C245" s="34" t="n"/>
-      <c r="D245" s="11">
-        <f>IF(C245="","",C245*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E245" s="12">
-        <f>IF(C245="","",C245-D245)</f>
-        <v/>
-      </c>
-      <c r="F245" s="19">
-        <f>IF(OR(B245="",C245=""),"",E245-B245)</f>
-        <v/>
-      </c>
-      <c r="G245" s="22">
-        <f>IF(OR(B245="",B245=0),"",F245/B245)</f>
-        <v/>
-      </c>
-      <c r="H245" s="13" t="n"/>
+      <c r="A245" s="45" t="inlineStr">
+        <is>
+          <t>MP9 | Sand Dashed 0.130889981985</t>
+        </is>
+      </c>
+      <c r="B245" s="54" t="n"/>
+      <c r="C245" s="55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D245" s="56">
+        <f>C245*$B$1</f>
+        <v/>
+      </c>
+      <c r="E245" s="57">
+        <f>C245-D245</f>
+        <v/>
+      </c>
+      <c r="F245" s="58">
+        <f>E245-B245</f>
+        <v/>
+      </c>
+      <c r="G245" s="59">
+        <f>F245/B245</f>
+        <v/>
+      </c>
+      <c r="H245" s="60" t="n"/>
     </row>
     <row r="246" ht="19.5" customHeight="1">
       <c r="A246" s="6" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -8968,26 +8968,32 @@
       <c r="H245" s="60" t="n"/>
     </row>
     <row r="246" ht="19.5" customHeight="1">
-      <c r="A246" s="6" t="n"/>
-      <c r="B246" s="26" t="n"/>
-      <c r="C246" s="33" t="n"/>
-      <c r="D246" s="7">
-        <f>IF(C246="","",C246*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E246" s="8">
-        <f>IF(C246="","",C246-D246)</f>
-        <v/>
-      </c>
-      <c r="F246" s="18">
-        <f>IF(OR(B246="",C246=""),"",E246-B246)</f>
-        <v/>
-      </c>
-      <c r="G246" s="21">
-        <f>IF(OR(B246="",B246=0),"",F246/B246)</f>
-        <v/>
-      </c>
-      <c r="H246" s="9" t="n"/>
+      <c r="A246" s="46" t="inlineStr">
+        <is>
+          <t>Nova | Walnut 0.325330734253</t>
+        </is>
+      </c>
+      <c r="B246" s="47" t="n"/>
+      <c r="C246" s="48" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D246" s="49">
+        <f>C246*$B$1</f>
+        <v/>
+      </c>
+      <c r="E246" s="50">
+        <f>C246-D246</f>
+        <v/>
+      </c>
+      <c r="F246" s="51">
+        <f>E246-B246</f>
+        <v/>
+      </c>
+      <c r="G246" s="52">
+        <f>F246/B246</f>
+        <v/>
+      </c>
+      <c r="H246" s="53" t="n"/>
     </row>
     <row r="247" ht="19.5" customHeight="1">
       <c r="A247" s="10" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -8996,26 +8996,32 @@
       <c r="H246" s="53" t="n"/>
     </row>
     <row r="247" ht="19.5" customHeight="1">
-      <c r="A247" s="10" t="n"/>
-      <c r="B247" s="27" t="n"/>
-      <c r="C247" s="34" t="n"/>
-      <c r="D247" s="11">
-        <f>IF(C247="","",C247*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E247" s="12">
-        <f>IF(C247="","",C247-D247)</f>
-        <v/>
-      </c>
-      <c r="F247" s="19">
-        <f>IF(OR(B247="",C247=""),"",E247-B247)</f>
-        <v/>
-      </c>
-      <c r="G247" s="22">
-        <f>IF(OR(B247="",B247=0),"",F247/B247)</f>
-        <v/>
-      </c>
-      <c r="H247" s="13" t="n"/>
+      <c r="A247" s="45" t="inlineStr">
+        <is>
+          <t>MAG 7 All star holo 0.353214085102</t>
+        </is>
+      </c>
+      <c r="B247" s="54" t="n"/>
+      <c r="C247" s="55" t="n">
+        <v>15</v>
+      </c>
+      <c r="D247" s="56">
+        <f>C247*$B$1</f>
+        <v/>
+      </c>
+      <c r="E247" s="57">
+        <f>C247-D247</f>
+        <v/>
+      </c>
+      <c r="F247" s="58">
+        <f>E247-B247</f>
+        <v/>
+      </c>
+      <c r="G247" s="59">
+        <f>F247/B247</f>
+        <v/>
+      </c>
+      <c r="H247" s="60" t="n"/>
     </row>
     <row r="248" ht="19.5" customHeight="1">
       <c r="A248" s="6" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -9024,48 +9024,60 @@
       <c r="H247" s="60" t="n"/>
     </row>
     <row r="248" ht="19.5" customHeight="1">
-      <c r="A248" s="6" t="n"/>
-      <c r="B248" s="26" t="n"/>
-      <c r="C248" s="33" t="n"/>
-      <c r="D248" s="7">
-        <f>IF(C248="","",C248*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E248" s="8">
-        <f>IF(C248="","",C248-D248)</f>
-        <v/>
-      </c>
-      <c r="F248" s="18">
-        <f>IF(OR(B248="",C248=""),"",E248-B248)</f>
-        <v/>
-      </c>
-      <c r="G248" s="21">
-        <f>IF(OR(B248="",B248=0),"",F248/B248)</f>
-        <v/>
-      </c>
-      <c r="H248" s="9" t="n"/>
+      <c r="A248" s="46" t="inlineStr">
+        <is>
+          <t>Mag7 Sand dune nip + fnatic kato 2015 gold (scrapped)</t>
+        </is>
+      </c>
+      <c r="B248" s="47" t="n"/>
+      <c r="C248" s="48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D248" s="49">
+        <f>C248*$B$1</f>
+        <v/>
+      </c>
+      <c r="E248" s="50">
+        <f>C248-D248</f>
+        <v/>
+      </c>
+      <c r="F248" s="51">
+        <f>E248-B248</f>
+        <v/>
+      </c>
+      <c r="G248" s="52">
+        <f>F248/B248</f>
+        <v/>
+      </c>
+      <c r="H248" s="53" t="n"/>
     </row>
     <row r="249" ht="19.5" customHeight="1">
-      <c r="A249" s="10" t="n"/>
-      <c r="B249" s="27" t="n"/>
-      <c r="C249" s="34" t="n"/>
-      <c r="D249" s="11">
-        <f>IF(C249="","",C249*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E249" s="12">
-        <f>IF(C249="","",C249-D249)</f>
-        <v/>
-      </c>
-      <c r="F249" s="19">
-        <f>IF(OR(B249="",C249=""),"",E249-B249)</f>
-        <v/>
-      </c>
-      <c r="G249" s="22">
-        <f>IF(OR(B249="",B249=0),"",F249/B249)</f>
-        <v/>
-      </c>
-      <c r="H249" s="13" t="n"/>
+      <c r="A249" s="45" t="inlineStr">
+        <is>
+          <t>UMP-45 | Indigo 0.324368596077</t>
+        </is>
+      </c>
+      <c r="B249" s="54" t="n"/>
+      <c r="C249" s="55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D249" s="56">
+        <f>C249*$B$1</f>
+        <v/>
+      </c>
+      <c r="E249" s="57">
+        <f>C249-D249</f>
+        <v/>
+      </c>
+      <c r="F249" s="58">
+        <f>E249-B249</f>
+        <v/>
+      </c>
+      <c r="G249" s="59">
+        <f>F249/B249</f>
+        <v/>
+      </c>
+      <c r="H249" s="60" t="n"/>
     </row>
     <row r="250" ht="19.5" customHeight="1">
       <c r="A250" s="6" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -9080,26 +9080,32 @@
       <c r="H249" s="60" t="n"/>
     </row>
     <row r="250" ht="19.5" customHeight="1">
-      <c r="A250" s="6" t="n"/>
-      <c r="B250" s="26" t="n"/>
-      <c r="C250" s="33" t="n"/>
-      <c r="D250" s="7">
-        <f>IF(C250="","",C250*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E250" s="8">
-        <f>IF(C250="","",C250-D250)</f>
-        <v/>
-      </c>
-      <c r="F250" s="18">
-        <f>IF(OR(B250="",C250=""),"",E250-B250)</f>
-        <v/>
-      </c>
-      <c r="G250" s="21">
-        <f>IF(OR(B250="",B250=0),"",F250/B250)</f>
-        <v/>
-      </c>
-      <c r="H250" s="9" t="n"/>
+      <c r="A250" s="46" t="inlineStr">
+        <is>
+          <t>P90  storm 0.62640</t>
+        </is>
+      </c>
+      <c r="B250" s="47" t="n"/>
+      <c r="C250" s="48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D250" s="49">
+        <f>C250*$B$1</f>
+        <v/>
+      </c>
+      <c r="E250" s="50">
+        <f>C250-D250</f>
+        <v/>
+      </c>
+      <c r="F250" s="51">
+        <f>E250-B250</f>
+        <v/>
+      </c>
+      <c r="G250" s="52">
+        <f>F250/B250</f>
+        <v/>
+      </c>
+      <c r="H250" s="53" t="n"/>
     </row>
     <row r="251" ht="19.5" customHeight="1">
       <c r="A251" s="10" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -9108,26 +9108,34 @@
       <c r="H250" s="53" t="n"/>
     </row>
     <row r="251" ht="19.5" customHeight="1">
-      <c r="A251" s="10" t="n"/>
-      <c r="B251" s="27" t="n"/>
-      <c r="C251" s="34" t="n"/>
-      <c r="D251" s="11">
-        <f>IF(C251="","",C251*$B$1)</f>
-        <v/>
-      </c>
-      <c r="E251" s="12">
-        <f>IF(C251="","",C251-D251)</f>
-        <v/>
-      </c>
-      <c r="F251" s="19">
-        <f>IF(OR(B251="",C251=""),"",E251-B251)</f>
-        <v/>
-      </c>
-      <c r="G251" s="22">
-        <f>IF(OR(B251="",B251=0),"",F251/B251)</f>
-        <v/>
-      </c>
-      <c r="H251" s="13" t="n"/>
+      <c r="A251" s="45" t="inlineStr">
+        <is>
+          <t>G3SG1 | Polar Camo 0.383077621460</t>
+        </is>
+      </c>
+      <c r="B251" s="54" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="C251" s="55" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D251" s="56">
+        <f>C251*$B$1</f>
+        <v/>
+      </c>
+      <c r="E251" s="57">
+        <f>C251-D251</f>
+        <v/>
+      </c>
+      <c r="F251" s="58">
+        <f>E251-B251</f>
+        <v/>
+      </c>
+      <c r="G251" s="59">
+        <f>F251/B251</f>
+        <v/>
+      </c>
+      <c r="H251" s="60" t="n"/>
     </row>
     <row r="252" ht="19.5" customHeight="1">
       <c r="A252" s="6" t="n"/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -230,7 +230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -398,6 +398,11 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -676,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1160"/>
+  <dimension ref="A1:AJ1163"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -28785,16 +28790,31 @@
     <row r="1147" ht="19.5" customHeight="1">
       <c r="A1147" s="14" t="inlineStr">
         <is>
-          <t>Total Items Sold</t>
-        </is>
-      </c>
-      <c r="B1147" s="30">
-        <f>COUNTA(A3:A1147)</f>
-        <v/>
-      </c>
-      <c r="C1147" s="35" t="n"/>
-      <c r="F1147" s="20" t="n"/>
-      <c r="G1147" s="23" t="n"/>
+          <t>Test Gun | Ghost Listing</t>
+        </is>
+      </c>
+      <c r="B1147" s="61" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C1147" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1147" s="63">
+        <f>C1147*$B$1</f>
+        <v/>
+      </c>
+      <c r="E1147" s="63">
+        <f>C1147-D1147</f>
+        <v/>
+      </c>
+      <c r="F1147" s="64">
+        <f>E1147-B1147</f>
+        <v/>
+      </c>
+      <c r="G1147" s="65">
+        <f>F1147/B1147</f>
+        <v/>
+      </c>
     </row>
     <row r="1148">
       <c r="A1148" s="14" t="inlineStr">

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -28790,14 +28790,14 @@
     <row r="1147" ht="19.5" customHeight="1">
       <c r="A1147" s="14" t="inlineStr">
         <is>
-          <t>Test Gun | Ghost Listing</t>
+          <t>AK-47 | Redline 0.229324132204</t>
         </is>
       </c>
       <c r="B1147" s="61" t="n">
-        <v>0.5</v>
+        <v>29.98</v>
       </c>
       <c r="C1147" s="62" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="D1147" s="63">
         <f>C1147*$B$1</f>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -28790,14 +28790,14 @@
     <row r="1147" ht="19.5" customHeight="1">
       <c r="A1147" s="14" t="inlineStr">
         <is>
-          <t>AK-47 | Redline 0.229324132204</t>
+          <t>MAG-7 | Irradiated Alert 0.384096920490</t>
         </is>
       </c>
       <c r="B1147" s="61" t="n">
-        <v>29.98</v>
+        <v>0.75</v>
       </c>
       <c r="C1147" s="62" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="D1147" s="63">
         <f>C1147*$B$1</f>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -28790,14 +28790,14 @@
     <row r="1147" ht="19.5" customHeight="1">
       <c r="A1147" s="14" t="inlineStr">
         <is>
-          <t>MAG-7 | Irradiated Alert 0.384096920490</t>
+          <t>AK-47 | Redline 0.229324132204</t>
         </is>
       </c>
       <c r="B1147" s="61" t="n">
-        <v>0.75</v>
+        <v>29.98</v>
       </c>
       <c r="C1147" s="62" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="D1147" s="63">
         <f>C1147*$B$1</f>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -28790,14 +28790,14 @@
     <row r="1147" ht="19.5" customHeight="1">
       <c r="A1147" s="14" t="inlineStr">
         <is>
-          <t>AK-47 | Redline 0.229324132204</t>
+          <t>Sawed off dick gold 0.266699075699</t>
         </is>
       </c>
       <c r="B1147" s="61" t="n">
-        <v>29.98</v>
+        <v>0.08</v>
       </c>
       <c r="C1147" s="62" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D1147" s="63">
         <f>C1147*$B$1</f>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -28790,14 +28790,14 @@
     <row r="1147" ht="19.5" customHeight="1">
       <c r="A1147" s="14" t="inlineStr">
         <is>
-          <t>Sawed off dick gold 0.266699075699</t>
+          <t>AK-47 | Redline 0.229324132204</t>
         </is>
       </c>
       <c r="B1147" s="61" t="n">
-        <v>0.08</v>
+        <v>29.98</v>
       </c>
       <c r="C1147" s="62" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D1147" s="63">
         <f>C1147*$B$1</f>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -28790,14 +28790,14 @@
     <row r="1147" ht="19.5" customHeight="1">
       <c r="A1147" s="14" t="inlineStr">
         <is>
-          <t>AK-47 | Redline 0.229324132204</t>
+          <t>MP9 | Storm 0.315184056759</t>
         </is>
       </c>
       <c r="B1147" s="61" t="n">
-        <v>29.98</v>
+        <v>0.24</v>
       </c>
       <c r="C1147" s="62" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="D1147" s="63">
         <f>C1147*$B$1</f>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -28790,14 +28790,14 @@
     <row r="1147" ht="19.5" customHeight="1">
       <c r="A1147" s="14" t="inlineStr">
         <is>
-          <t>MP9 | Storm 0.315184056759</t>
+          <t>MAG-7 | Sand Dune 0.386119425297</t>
         </is>
       </c>
       <c r="B1147" s="61" t="n">
-        <v>0.24</v>
+        <v>7.17</v>
       </c>
       <c r="C1147" s="62" t="n">
-        <v>12</v>
+        <v>13.2</v>
       </c>
       <c r="D1147" s="63">
         <f>C1147*$B$1</f>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -28790,14 +28790,14 @@
     <row r="1147" ht="19.5" customHeight="1">
       <c r="A1147" s="14" t="inlineStr">
         <is>
-          <t>MAG-7 | Sand Dune 0.386119425297</t>
+          <t>AK-47 | Redline 0.229324132204</t>
         </is>
       </c>
       <c r="B1147" s="61" t="n">
-        <v>7.17</v>
+        <v>29.98</v>
       </c>
       <c r="C1147" s="62" t="n">
-        <v>13.2</v>
+        <v>42</v>
       </c>
       <c r="D1147" s="63">
         <f>C1147*$B$1</f>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -28790,14 +28790,14 @@
     <row r="1147" ht="19.5" customHeight="1">
       <c r="A1147" s="14" t="inlineStr">
         <is>
-          <t>AK-47 | Redline 0.229324132204</t>
+          <t>M249 | Contrast Spray 0.283993452787 Kenny Gold krakow</t>
         </is>
       </c>
       <c r="B1147" s="61" t="n">
-        <v>29.98</v>
+        <v>6.75</v>
       </c>
       <c r="C1147" s="62" t="n">
-        <v>42</v>
+        <v>9.5</v>
       </c>
       <c r="D1147" s="63">
         <f>C1147*$B$1</f>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -28790,14 +28790,14 @@
     <row r="1147" ht="19.5" customHeight="1">
       <c r="A1147" s="14" t="inlineStr">
         <is>
-          <t>M249 | Contrast Spray 0.283993452787 Kenny Gold krakow</t>
+          <t>Nova | Walnut 0.549327969551</t>
         </is>
       </c>
       <c r="B1147" s="61" t="n">
-        <v>6.75</v>
+        <v>0.47</v>
       </c>
       <c r="C1147" s="62" t="n">
-        <v>9.5</v>
+        <v>2.6</v>
       </c>
       <c r="D1147" s="63">
         <f>C1147*$B$1</f>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -9531,9 +9531,17 @@
       <c r="H259" s="9" t="n"/>
     </row>
     <row r="260" ht="19.5" customHeight="1" s="49">
-      <c r="A260" s="10" t="n"/>
-      <c r="B260" s="25" t="n"/>
-      <c r="C260" s="30" t="n"/>
+      <c r="A260" s="10" t="inlineStr">
+        <is>
+          <t>USP-S | Royal Blue 0.383412957191</t>
+        </is>
+      </c>
+      <c r="B260" s="25" t="n">
+        <v>0.1268</v>
+      </c>
+      <c r="C260" s="30" t="n">
+        <v>16</v>
+      </c>
       <c r="D260" s="11">
         <f>IF(C260="","",C260*$B$1)</f>
         <v/>
@@ -9553,9 +9561,17 @@
       <c r="H260" s="13" t="n"/>
     </row>
     <row r="261" ht="19.5" customHeight="1" s="49">
-      <c r="A261" s="6" t="n"/>
-      <c r="B261" s="24" t="n"/>
-      <c r="C261" s="29" t="n"/>
+      <c r="A261" s="6" t="inlineStr">
+        <is>
+          <t>Nova | Walnut 0.370155155659</t>
+        </is>
+      </c>
+      <c r="B261" s="24" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="C261" s="29" t="n">
+        <v>2.8</v>
+      </c>
       <c r="D261" s="7">
         <f>IF(C261="","",C261*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -9591,9 +9591,17 @@
       <c r="H261" s="9" t="n"/>
     </row>
     <row r="262" ht="19.5" customHeight="1" s="49">
-      <c r="A262" s="10" t="n"/>
-      <c r="B262" s="25" t="n"/>
-      <c r="C262" s="30" t="n"/>
+      <c r="A262" s="10" t="inlineStr">
+        <is>
+          <t>Sawed-Off | Irradiated Alert 3dMax kato gold (not full set) 0.392642647028</t>
+        </is>
+      </c>
+      <c r="B262" s="25" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="C262" s="30" t="n">
+        <v>5.95</v>
+      </c>
       <c r="D262" s="11">
         <f>IF(C262="","",C262*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -9621,9 +9621,17 @@
       <c r="H262" s="13" t="n"/>
     </row>
     <row r="263" ht="19.5" customHeight="1" s="49">
-      <c r="A263" s="6" t="n"/>
-      <c r="B263" s="24" t="n"/>
-      <c r="C263" s="29" t="n"/>
+      <c r="A263" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M249 | Contrast Spray 0.207938030362 Kenny Gold krakow </t>
+        </is>
+      </c>
+      <c r="B263" s="24" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="C263" s="29" t="n">
+        <v>9.65</v>
+      </c>
       <c r="D263" s="7">
         <f>IF(C263="","",C263*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -9651,9 +9651,17 @@
       <c r="H263" s="9" t="n"/>
     </row>
     <row r="264" ht="19.5" customHeight="1" s="49">
-      <c r="A264" s="10" t="n"/>
-      <c r="B264" s="25" t="n"/>
-      <c r="C264" s="30" t="n"/>
+      <c r="A264" s="10" t="inlineStr">
+        <is>
+          <t>MAG-7 | Sand Dune .160451918840</t>
+        </is>
+      </c>
+      <c r="B264" s="25" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="C264" s="30" t="n">
+        <v>2.6</v>
+      </c>
       <c r="D264" s="11">
         <f>IF(C264="","",C264*$B$1)</f>
         <v/>
@@ -9673,9 +9681,17 @@
       <c r="H264" s="13" t="n"/>
     </row>
     <row r="265" ht="19.5" customHeight="1" s="49">
-      <c r="A265" s="6" t="n"/>
-      <c r="B265" s="24" t="n"/>
-      <c r="C265" s="29" t="n"/>
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>AUG | Sweeper 0.540548026562</t>
+        </is>
+      </c>
+      <c r="B265" s="24" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C265" s="29" t="n">
+        <v>1.9</v>
+      </c>
       <c r="D265" s="7">
         <f>IF(C265="","",C265*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -9711,9 +9711,17 @@
       <c r="H265" s="9" t="n"/>
     </row>
     <row r="266" ht="19.5" customHeight="1" s="49">
-      <c r="A266" s="10" t="n"/>
-      <c r="B266" s="25" t="n"/>
-      <c r="C266" s="30" t="n"/>
+      <c r="A266" s="10" t="inlineStr">
+        <is>
+          <t>Sawed-Off | Sage Spray 0.349741399288</t>
+        </is>
+      </c>
+      <c r="B266" s="25" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="C266" s="30" t="n">
+        <v>9.5</v>
+      </c>
       <c r="D266" s="11">
         <f>IF(C266="","",C266*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -9741,9 +9741,17 @@
       <c r="H266" s="13" t="n"/>
     </row>
     <row r="267" ht="19.5" customHeight="1" s="49">
-      <c r="A267" s="6" t="n"/>
-      <c r="B267" s="24" t="n"/>
-      <c r="C267" s="29" t="n"/>
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>G3SG1 | Safari Mesh 0.128206089139</t>
+        </is>
+      </c>
+      <c r="B267" s="24" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="C267" s="29" t="n">
+        <v>5.25</v>
+      </c>
       <c r="D267" s="7">
         <f>IF(C267="","",C267*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -9771,9 +9771,17 @@
       <c r="H267" s="9" t="n"/>
     </row>
     <row r="268" ht="19.5" customHeight="1" s="49">
-      <c r="A268" s="10" t="n"/>
-      <c r="B268" s="25" t="n"/>
-      <c r="C268" s="30" t="n"/>
+      <c r="A268" s="10" t="inlineStr">
+        <is>
+          <t>UMP-45 | Urban DDPAT</t>
+        </is>
+      </c>
+      <c r="B268" s="25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="C268" s="30" t="n">
+        <v>10</v>
+      </c>
       <c r="D268" s="11">
         <f>IF(C268="","",C268*$B$1)</f>
         <v/>
@@ -9793,9 +9801,17 @@
       <c r="H268" s="13" t="n"/>
     </row>
     <row r="269" ht="19.5" customHeight="1" s="49">
-      <c r="A269" s="6" t="n"/>
-      <c r="B269" s="24" t="n"/>
-      <c r="C269" s="29" t="n"/>
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>AUG | Colony 0.386405706406</t>
+        </is>
+      </c>
+      <c r="B269" s="24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C269" s="29" t="n">
+        <v>2.95</v>
+      </c>
       <c r="D269" s="7">
         <f>IF(C269="","",C269*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -9831,9 +9831,17 @@
       <c r="H269" s="9" t="n"/>
     </row>
     <row r="270" ht="19.5" customHeight="1" s="49">
-      <c r="A270" s="10" t="n"/>
-      <c r="B270" s="25" t="n"/>
-      <c r="C270" s="30" t="n"/>
+      <c r="A270" s="10" t="inlineStr">
+        <is>
+          <t>Sawed-Off | Irradiated Alert 0.781168520451</t>
+        </is>
+      </c>
+      <c r="B270" s="25" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="C270" s="30" t="n">
+        <v>16.8</v>
+      </c>
       <c r="D270" s="11">
         <f>IF(C270="","",C270*$B$1)</f>
         <v/>
@@ -9853,9 +9861,17 @@
       <c r="H270" s="13" t="n"/>
     </row>
     <row r="271" ht="19.5" customHeight="1" s="49">
-      <c r="A271" s="6" t="n"/>
-      <c r="B271" s="24" t="n"/>
-      <c r="C271" s="29" t="n"/>
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>PP-Bizon | Irradiated Alert 0.797088861465</t>
+        </is>
+      </c>
+      <c r="B271" s="24" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="C271" s="29" t="n">
+        <v>18</v>
+      </c>
       <c r="D271" s="7">
         <f>IF(C271="","",C271*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -9891,9 +9891,17 @@
       <c r="H271" s="9" t="n"/>
     </row>
     <row r="272" ht="19.5" customHeight="1" s="49">
-      <c r="A272" s="10" t="n"/>
-      <c r="B272" s="25" t="n"/>
-      <c r="C272" s="30" t="n"/>
+      <c r="A272" s="10" t="inlineStr">
+        <is>
+          <t>Sawed-Off | Snake Camo 0.250000000000</t>
+        </is>
+      </c>
+      <c r="B272" s="25" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C272" s="30" t="n">
+        <v>1.2</v>
+      </c>
       <c r="D272" s="11">
         <f>IF(C272="","",C272*$B$1)</f>
         <v/>
@@ -9913,9 +9921,17 @@
       <c r="H272" s="13" t="n"/>
     </row>
     <row r="273" ht="19.5" customHeight="1" s="49">
-      <c r="A273" s="6" t="n"/>
-      <c r="B273" s="24" t="n"/>
-      <c r="C273" s="29" t="n"/>
+      <c r="A273" s="6" t="inlineStr">
+        <is>
+          <t>PP-Bizon | Urban Dashed 0.368814378977</t>
+        </is>
+      </c>
+      <c r="B273" s="24" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C273" s="29" t="n">
+        <v>1.7</v>
+      </c>
       <c r="D273" s="7">
         <f>IF(C273="","",C273*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -9951,9 +9951,17 @@
       <c r="H273" s="9" t="n"/>
     </row>
     <row r="274" ht="19.5" customHeight="1" s="49">
-      <c r="A274" s="10" t="n"/>
-      <c r="B274" s="25" t="n"/>
-      <c r="C274" s="30" t="n"/>
+      <c r="A274" s="10" t="inlineStr">
+        <is>
+          <t>UMP-45 | Urban DDPAT</t>
+        </is>
+      </c>
+      <c r="B274" s="25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="C274" s="30" t="n">
+        <v>10</v>
+      </c>
       <c r="D274" s="11">
         <f>IF(C274="","",C274*$B$1)</f>
         <v/>
@@ -9973,9 +9981,17 @@
       <c r="H274" s="13" t="n"/>
     </row>
     <row r="275" ht="19.5" customHeight="1" s="49">
-      <c r="A275" s="6" t="n"/>
-      <c r="B275" s="24" t="n"/>
-      <c r="C275" s="29" t="n"/>
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>P250 | Bone Mask</t>
+        </is>
+      </c>
+      <c r="B275" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="C275" s="29" t="n">
+        <v>43.6</v>
+      </c>
       <c r="D275" s="7">
         <f>IF(C275="","",C275*$B$1)</f>
         <v/>
@@ -9995,9 +10011,17 @@
       <c r="H275" s="9" t="n"/>
     </row>
     <row r="276" ht="19.5" customHeight="1" s="49">
-      <c r="A276" s="10" t="n"/>
-      <c r="B276" s="25" t="n"/>
-      <c r="C276" s="30" t="n"/>
+      <c r="A276" s="10" t="inlineStr">
+        <is>
+          <t>Tec-9 | Army Mesh</t>
+        </is>
+      </c>
+      <c r="B276" s="25" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="C276" s="30" t="n">
+        <v>43.4</v>
+      </c>
       <c r="D276" s="11">
         <f>IF(C276="","",C276*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10041,9 +10041,17 @@
       <c r="H276" s="13" t="n"/>
     </row>
     <row r="277" ht="19.5" customHeight="1" s="49">
-      <c r="A277" s="6" t="n"/>
-      <c r="B277" s="24" t="n"/>
-      <c r="C277" s="29" t="n"/>
+      <c r="A277" s="6" t="inlineStr">
+        <is>
+          <t>Nova | Walnut 0.689443826675</t>
+        </is>
+      </c>
+      <c r="B277" s="24" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="C277" s="29" t="n">
+        <v>8</v>
+      </c>
       <c r="D277" s="7">
         <f>IF(C277="","",C277*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10071,9 +10071,17 @@
       <c r="H277" s="9" t="n"/>
     </row>
     <row r="278" ht="19.5" customHeight="1" s="49">
-      <c r="A278" s="10" t="n"/>
-      <c r="B278" s="25" t="n"/>
-      <c r="C278" s="30" t="n"/>
+      <c r="A278" s="10" t="inlineStr">
+        <is>
+          <t>Nova | Predator 0.378227680922</t>
+        </is>
+      </c>
+      <c r="B278" s="25" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C278" s="30" t="n">
+        <v>3</v>
+      </c>
       <c r="D278" s="11">
         <f>IF(C278="","",C278*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10101,9 +10101,17 @@
       <c r="H278" s="13" t="n"/>
     </row>
     <row r="279" ht="19.5" customHeight="1" s="49">
-      <c r="A279" s="6" t="n"/>
-      <c r="B279" s="24" t="n"/>
-      <c r="C279" s="29" t="n"/>
+      <c r="A279" s="6" t="inlineStr">
+        <is>
+          <t>MAG-7 | Sand Dune 0.152819916606</t>
+        </is>
+      </c>
+      <c r="B279" s="24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C279" s="29" t="n">
+        <v>2.5</v>
+      </c>
       <c r="D279" s="7">
         <f>IF(C279="","",C279*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10131,9 +10131,17 @@
       <c r="H279" s="9" t="n"/>
     </row>
     <row r="280" ht="19.5" customHeight="1" s="49">
-      <c r="A280" s="10" t="n"/>
-      <c r="B280" s="25" t="n"/>
-      <c r="C280" s="30" t="n"/>
+      <c r="A280" s="10" t="inlineStr">
+        <is>
+          <t>ESL One Katowice 2015 Dust II Souvenir Package Navi Vs Envy</t>
+        </is>
+      </c>
+      <c r="B280" s="25" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="C280" s="30" t="n">
+        <v>53</v>
+      </c>
       <c r="D280" s="11">
         <f>IF(C280="","",C280*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10161,9 +10161,17 @@
       <c r="H280" s="13" t="n"/>
     </row>
     <row r="281" ht="19.5" customHeight="1" s="49">
-      <c r="A281" s="6" t="n"/>
-      <c r="B281" s="24" t="n"/>
-      <c r="C281" s="29" t="n"/>
+      <c r="A281" s="6" t="inlineStr">
+        <is>
+          <t>SSG Abyss Highfloat 4x liquid fire</t>
+        </is>
+      </c>
+      <c r="B281" s="24" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="C281" s="29" t="n">
+        <v>7</v>
+      </c>
       <c r="D281" s="7">
         <f>IF(C281="","",C281*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10191,9 +10191,17 @@
       <c r="H281" s="9" t="n"/>
     </row>
     <row r="282" ht="19.5" customHeight="1" s="49">
-      <c r="A282" s="10" t="n"/>
-      <c r="B282" s="25" t="n"/>
-      <c r="C282" s="30" t="n"/>
+      <c r="A282" s="10" t="inlineStr">
+        <is>
+          <t>USP-S | Blueprint 0.299943238497</t>
+        </is>
+      </c>
+      <c r="B282" s="25" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="C282" s="30" t="n">
+        <v>16</v>
+      </c>
       <c r="D282" s="11">
         <f>IF(C282="","",C282*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10221,9 +10221,17 @@
       <c r="H282" s="13" t="n"/>
     </row>
     <row r="283" ht="19.5" customHeight="1" s="49">
-      <c r="A283" s="6" t="n"/>
-      <c r="B283" s="24" t="n"/>
-      <c r="C283" s="29" t="n"/>
+      <c r="A283" s="6" t="inlineStr">
+        <is>
+          <t>Nova | Walnut 0.366425216198</t>
+        </is>
+      </c>
+      <c r="B283" s="24" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="C283" s="29" t="n">
+        <v>3.1</v>
+      </c>
       <c r="D283" s="7">
         <f>IF(C283="","",C283*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10251,9 +10251,17 @@
       <c r="H283" s="9" t="n"/>
     </row>
     <row r="284" ht="19.5" customHeight="1" s="49">
-      <c r="A284" s="10" t="n"/>
-      <c r="B284" s="25" t="n"/>
-      <c r="C284" s="30" t="n"/>
+      <c r="A284" s="10" t="inlineStr">
+        <is>
+          <t>UMP-45 | Indigo 0.252622604370</t>
+        </is>
+      </c>
+      <c r="B284" s="25" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C284" s="30" t="n">
+        <v>6</v>
+      </c>
       <c r="D284" s="11">
         <f>IF(C284="","",C284*$B$1)</f>
         <v/>
@@ -10273,9 +10281,17 @@
       <c r="H284" s="13" t="n"/>
     </row>
     <row r="285" ht="19.5" customHeight="1" s="49">
-      <c r="A285" s="6" t="n"/>
-      <c r="B285" s="24" t="n"/>
-      <c r="C285" s="29" t="n"/>
+      <c r="A285" s="6" t="inlineStr">
+        <is>
+          <t>P2000 | Grassland 0.299911409616</t>
+        </is>
+      </c>
+      <c r="B285" s="24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C285" s="29" t="n">
+        <v>4.8</v>
+      </c>
       <c r="D285" s="7">
         <f>IF(C285="","",C285*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10311,9 +10311,17 @@
       <c r="H285" s="9" t="n"/>
     </row>
     <row r="286" ht="19.5" customHeight="1" s="49">
-      <c r="A286" s="10" t="n"/>
-      <c r="B286" s="25" t="n"/>
-      <c r="C286" s="30" t="n"/>
+      <c r="A286" s="10" t="inlineStr">
+        <is>
+          <t>Desert Eagle | Urban DDPAT 0.240540176630 Krakow MVPless</t>
+        </is>
+      </c>
+      <c r="B286" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C286" s="30" t="n">
+        <v>11.1</v>
+      </c>
       <c r="D286" s="11">
         <f>IF(C286="","",C286*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10341,9 +10341,17 @@
       <c r="H286" s="13" t="n"/>
     </row>
     <row r="287" ht="19.5" customHeight="1" s="49">
-      <c r="A287" s="6" t="n"/>
-      <c r="B287" s="24" t="n"/>
-      <c r="C287" s="29" t="n"/>
+      <c r="A287" s="6" t="inlineStr">
+        <is>
+          <t>MAG-7 | Sand Dune 0.207860738039</t>
+        </is>
+      </c>
+      <c r="B287" s="24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C287" s="29" t="n">
+        <v>1.8</v>
+      </c>
       <c r="D287" s="7">
         <f>IF(C287="","",C287*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10371,9 +10371,17 @@
       <c r="H287" s="9" t="n"/>
     </row>
     <row r="288" ht="19.5" customHeight="1" s="49">
-      <c r="A288" s="10" t="n"/>
-      <c r="B288" s="25" t="n"/>
-      <c r="C288" s="30" t="n"/>
+      <c r="A288" s="10" t="inlineStr">
+        <is>
+          <t>Glock-18 | Shinobu</t>
+        </is>
+      </c>
+      <c r="B288" s="25" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="C288" s="30" t="n">
+        <v>12</v>
+      </c>
       <c r="D288" s="11">
         <f>IF(C288="","",C288*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10320,7 +10320,7 @@
         <v>4</v>
       </c>
       <c r="C286" s="30" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="D286" s="11">
         <f>IF(C286="","",C286*$B$1)</f>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10401,9 +10401,17 @@
       <c r="H288" s="13" t="n"/>
     </row>
     <row r="289" ht="19.5" customHeight="1" s="49">
-      <c r="A289" s="6" t="n"/>
-      <c r="B289" s="24" t="n"/>
-      <c r="C289" s="29" t="n"/>
+      <c r="A289" s="6" t="inlineStr">
+        <is>
+          <t>MAG-7 | Irradiated Alert 0.795957326889</t>
+        </is>
+      </c>
+      <c r="B289" s="24" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="C289" s="29" t="n">
+        <v>16</v>
+      </c>
       <c r="D289" s="7">
         <f>IF(C289="","",C289*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10431,9 +10431,17 @@
       <c r="H289" s="9" t="n"/>
     </row>
     <row r="290" ht="19.5" customHeight="1" s="49">
-      <c r="A290" s="10" t="n"/>
-      <c r="B290" s="25" t="n"/>
-      <c r="C290" s="30" t="n"/>
+      <c r="A290" s="10" t="inlineStr">
+        <is>
+          <t>Sawed-Off | Irradiated Alert 0.280755698681</t>
+        </is>
+      </c>
+      <c r="B290" s="25" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="C290" s="30" t="n">
+        <v>13.5</v>
+      </c>
       <c r="D290" s="11">
         <f>IF(C290="","",C290*$B$1)</f>
         <v/>
@@ -10453,9 +10461,17 @@
       <c r="H290" s="13" t="n"/>
     </row>
     <row r="291" ht="19.5" customHeight="1" s="49">
-      <c r="A291" s="6" t="n"/>
-      <c r="B291" s="24" t="n"/>
-      <c r="C291" s="29" t="n"/>
+      <c r="A291" s="6" t="inlineStr">
+        <is>
+          <t>AUG | Colony 0.136085629463</t>
+        </is>
+      </c>
+      <c r="B291" s="24" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="C291" s="29" t="n">
+        <v>3.1</v>
+      </c>
       <c r="D291" s="7">
         <f>IF(C291="","",C291*$B$1)</f>
         <v/>
@@ -10475,9 +10491,17 @@
       <c r="H291" s="9" t="n"/>
     </row>
     <row r="292" ht="19.5" customHeight="1" s="49">
-      <c r="A292" s="10" t="n"/>
-      <c r="B292" s="25" t="n"/>
-      <c r="C292" s="30" t="n"/>
+      <c r="A292" s="10" t="inlineStr">
+        <is>
+          <t>MAG-7 | Sand Dune 0.356272578239</t>
+        </is>
+      </c>
+      <c r="B292" s="25" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C292" s="30" t="n">
+        <v>1.9</v>
+      </c>
       <c r="D292" s="11">
         <f>IF(C292="","",C292*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10521,9 +10521,17 @@
       <c r="H292" s="13" t="n"/>
     </row>
     <row r="293" ht="19.5" customHeight="1" s="49">
-      <c r="A293" s="6" t="n"/>
-      <c r="B293" s="24" t="n"/>
-      <c r="C293" s="29" t="n"/>
+      <c r="A293" s="6" t="inlineStr">
+        <is>
+          <t>R8 Revolver | Nitro 0.144783005118</t>
+        </is>
+      </c>
+      <c r="B293" s="24" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C293" s="29" t="n">
+        <v>12.75</v>
+      </c>
       <c r="D293" s="7">
         <f>IF(C293="","",C293*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10551,9 +10551,17 @@
       <c r="H293" s="9" t="n"/>
     </row>
     <row r="294" ht="19.5" customHeight="1" s="49">
-      <c r="A294" s="10" t="n"/>
-      <c r="B294" s="25" t="n"/>
-      <c r="C294" s="30" t="n"/>
+      <c r="A294" s="10" t="inlineStr">
+        <is>
+          <t>Desert Eagle | Urban DDPAT 0.458946824074</t>
+        </is>
+      </c>
+      <c r="B294" s="25" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C294" s="30" t="n">
+        <v>6</v>
+      </c>
       <c r="D294" s="11">
         <f>IF(C294="","",C294*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10581,9 +10581,17 @@
       <c r="H294" s="13" t="n"/>
     </row>
     <row r="295" ht="19.5" customHeight="1" s="49">
-      <c r="A295" s="6" t="n"/>
-      <c r="B295" s="24" t="n"/>
-      <c r="C295" s="29" t="n"/>
+      <c r="A295" s="6" t="inlineStr">
+        <is>
+          <t>G3SG1 | Desert Storm 0.181939452887</t>
+        </is>
+      </c>
+      <c r="B295" s="24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C295" s="29" t="n">
+        <v>2.6</v>
+      </c>
       <c r="D295" s="7">
         <f>IF(C295="","",C295*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10611,9 +10611,17 @@
       <c r="H295" s="9" t="n"/>
     </row>
     <row r="296" ht="19.5" customHeight="1" s="49">
-      <c r="A296" s="10" t="n"/>
-      <c r="B296" s="25" t="n"/>
-      <c r="C296" s="30" t="n"/>
+      <c r="A296" s="10" t="inlineStr">
+        <is>
+          <t>Sawed-Off | Irradiated Alert 0.376527249813</t>
+        </is>
+      </c>
+      <c r="B296" s="25" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="C296" s="30" t="n">
+        <v>14</v>
+      </c>
       <c r="D296" s="11">
         <f>IF(C296="","",C296*$B$1)</f>
         <v/>
@@ -10633,9 +10641,17 @@
       <c r="H296" s="13" t="n"/>
     </row>
     <row r="297" ht="19.5" customHeight="1" s="49">
-      <c r="A297" s="6" t="n"/>
-      <c r="B297" s="24" t="n"/>
-      <c r="C297" s="29" t="n"/>
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>PP-Bizon | Irradiated Alert 0.790591835976</t>
+        </is>
+      </c>
+      <c r="B297" s="24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C297" s="29" t="n">
+        <v>8.1</v>
+      </c>
       <c r="D297" s="7">
         <f>IF(C297="","",C297*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10671,9 +10671,17 @@
       <c r="H297" s="9" t="n"/>
     </row>
     <row r="298" ht="19.5" customHeight="1" s="49">
-      <c r="A298" s="10" t="n"/>
-      <c r="B298" s="25" t="n"/>
-      <c r="C298" s="30" t="n"/>
+      <c r="A298" s="10" t="inlineStr">
+        <is>
+          <t>PP-Bizon | Irradiated Alert 0.365386217833</t>
+        </is>
+      </c>
+      <c r="B298" s="25" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C298" s="30" t="n">
+        <v>2.5</v>
+      </c>
       <c r="D298" s="11">
         <f>IF(C298="","",C298*$B$1)</f>
         <v/>
@@ -10693,9 +10701,17 @@
       <c r="H298" s="13" t="n"/>
     </row>
     <row r="299" ht="19.5" customHeight="1" s="49">
-      <c r="A299" s="6" t="n"/>
-      <c r="B299" s="24" t="n"/>
-      <c r="C299" s="29" t="n"/>
+      <c r="A299" s="6" t="inlineStr">
+        <is>
+          <t>Sawed-Off | Irradiated Alert 0.376977741718</t>
+        </is>
+      </c>
+      <c r="B299" s="24" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="C299" s="29" t="n">
+        <v>8.1</v>
+      </c>
       <c r="D299" s="7">
         <f>IF(C299="","",C299*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10731,9 +10731,17 @@
       <c r="H299" s="9" t="n"/>
     </row>
     <row r="300" ht="19.5" customHeight="1" s="49">
-      <c r="A300" s="10" t="n"/>
-      <c r="B300" s="25" t="n"/>
-      <c r="C300" s="30" t="n"/>
+      <c r="A300" s="10" t="inlineStr">
+        <is>
+          <t>P90 | Sand Spray 0.358815312386 Kato foils best pos</t>
+        </is>
+      </c>
+      <c r="B300" s="25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C300" s="30" t="n">
+        <v>30</v>
+      </c>
       <c r="D300" s="11">
         <f>IF(C300="","",C300*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10761,9 +10761,17 @@
       <c r="H300" s="13" t="n"/>
     </row>
     <row r="301" ht="19.5" customHeight="1" s="49">
-      <c r="A301" s="6" t="n"/>
-      <c r="B301" s="24" t="n"/>
-      <c r="C301" s="29" t="n"/>
+      <c r="A301" s="6" t="inlineStr">
+        <is>
+          <t>AK-47 | Slate 0.147975370288</t>
+        </is>
+      </c>
+      <c r="B301" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C301" s="29" t="n">
+        <v>9.5</v>
+      </c>
       <c r="D301" s="7">
         <f>IF(C301="","",C301*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10791,9 +10791,17 @@
       <c r="H301" s="9" t="n"/>
     </row>
     <row r="302" ht="19.5" customHeight="1" s="49">
-      <c r="A302" s="10" t="n"/>
-      <c r="B302" s="25" t="n"/>
-      <c r="C302" s="30" t="n"/>
+      <c r="A302" s="10" t="inlineStr">
+        <is>
+          <t>MP9 | Sand Dashed 0.368502467871</t>
+        </is>
+      </c>
+      <c r="B302" s="25" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C302" s="30" t="n">
+        <v>3.1</v>
+      </c>
       <c r="D302" s="11">
         <f>IF(C302="","",C302*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10530,7 +10530,7 @@
         <v>0.26</v>
       </c>
       <c r="C293" s="29" t="n">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="D293" s="7">
         <f>IF(C293="","",C293*$B$1)</f>
@@ -10740,7 +10740,7 @@
         <v>13.5</v>
       </c>
       <c r="C300" s="30" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D300" s="11">
         <f>IF(C300="","",C300*$B$1)</f>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10821,9 +10821,15 @@
       <c r="H302" s="13" t="n"/>
     </row>
     <row r="303" ht="19.5" customHeight="1" s="49">
-      <c r="A303" s="6" t="n"/>
+      <c r="A303" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glock-18 | Wraiths Low float 5X battlescared 0.000269792916 </t>
+        </is>
+      </c>
       <c r="B303" s="24" t="n"/>
-      <c r="C303" s="29" t="n"/>
+      <c r="C303" s="29" t="n">
+        <v>35</v>
+      </c>
       <c r="D303" s="7">
         <f>IF(C303="","",C303*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10821,15 +10821,9 @@
       <c r="H302" s="13" t="n"/>
     </row>
     <row r="303" ht="19.5" customHeight="1" s="49">
-      <c r="A303" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Glock-18 | Wraiths Low float 5X battlescared 0.000269792916 </t>
-        </is>
-      </c>
+      <c r="A303" s="6" t="n"/>
       <c r="B303" s="24" t="n"/>
-      <c r="C303" s="29" t="n">
-        <v>35</v>
-      </c>
+      <c r="C303" s="29" t="n"/>
       <c r="D303" s="7">
         <f>IF(C303="","",C303*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10821,9 +10821,17 @@
       <c r="H302" s="13" t="n"/>
     </row>
     <row r="303" ht="19.5" customHeight="1" s="49">
-      <c r="A303" s="6" t="n"/>
-      <c r="B303" s="24" t="n"/>
-      <c r="C303" s="29" t="n"/>
+      <c r="A303" s="6" t="inlineStr">
+        <is>
+          <t>M4A1-S | Black Lotus 0.262870907784</t>
+        </is>
+      </c>
+      <c r="B303" s="24" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="C303" s="29" t="n">
+        <v>21</v>
+      </c>
       <c r="D303" s="7">
         <f>IF(C303="","",C303*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10851,9 +10851,17 @@
       <c r="H303" s="9" t="n"/>
     </row>
     <row r="304" ht="19.5" customHeight="1" s="49">
-      <c r="A304" s="10" t="n"/>
-      <c r="B304" s="25" t="n"/>
-      <c r="C304" s="30" t="n"/>
+      <c r="A304" s="10" t="inlineStr">
+        <is>
+          <t>Dual Berettas | Colony 0.216993585229</t>
+        </is>
+      </c>
+      <c r="B304" s="25" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C304" s="30" t="n">
+        <v>2.2</v>
+      </c>
       <c r="D304" s="11">
         <f>IF(C304="","",C304*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10881,9 +10881,17 @@
       <c r="H304" s="13" t="n"/>
     </row>
     <row r="305" ht="19.5" customHeight="1" s="49">
-      <c r="A305" s="6" t="n"/>
-      <c r="B305" s="24" t="n"/>
-      <c r="C305" s="29" t="n"/>
+      <c r="A305" s="6" t="inlineStr">
+        <is>
+          <t>P90 Facility Negative Faceit Gold</t>
+        </is>
+      </c>
+      <c r="B305" s="24" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="C305" s="29" t="n">
+        <v>4.15</v>
+      </c>
       <c r="D305" s="7">
         <f>IF(C305="","",C305*$B$1)</f>
         <v/>
@@ -10903,9 +10911,17 @@
       <c r="H305" s="9" t="n"/>
     </row>
     <row r="306" ht="19.5" customHeight="1" s="49">
-      <c r="A306" s="10" t="n"/>
-      <c r="B306" s="25" t="n"/>
-      <c r="C306" s="30" t="n"/>
+      <c r="A306" s="10" t="inlineStr">
+        <is>
+          <t>MP9 | Sand Dashed 0.305512368679</t>
+        </is>
+      </c>
+      <c r="B306" s="25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C306" s="30" t="n">
+        <v>2.9</v>
+      </c>
       <c r="D306" s="11">
         <f>IF(C306="","",C306*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10941,9 +10941,17 @@
       <c r="H306" s="13" t="n"/>
     </row>
     <row r="307" ht="19.5" customHeight="1" s="49">
-      <c r="A307" s="6" t="n"/>
-      <c r="B307" s="24" t="n"/>
-      <c r="C307" s="29" t="n"/>
+      <c r="A307" s="6" t="inlineStr">
+        <is>
+          <t>Sawed-Off | Snake Camo 0.250000000000 (2)</t>
+        </is>
+      </c>
+      <c r="B307" s="24" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C307" s="29" t="n">
+        <v>1.2</v>
+      </c>
       <c r="D307" s="7">
         <f>IF(C307="","",C307*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -10971,9 +10971,17 @@
       <c r="H307" s="9" t="n"/>
     </row>
     <row r="308" ht="19.5" customHeight="1" s="49">
-      <c r="A308" s="10" t="n"/>
-      <c r="B308" s="25" t="n"/>
-      <c r="C308" s="30" t="n"/>
+      <c r="A308" s="10" t="inlineStr">
+        <is>
+          <t>M249 | Contrast Spray 0.165465533733</t>
+        </is>
+      </c>
+      <c r="B308" s="25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C308" s="30" t="n">
+        <v>2.7</v>
+      </c>
       <c r="D308" s="11">
         <f>IF(C308="","",C308*$B$1)</f>
         <v/>
@@ -10993,9 +11001,17 @@
       <c r="H308" s="13" t="n"/>
     </row>
     <row r="309" ht="19.5" customHeight="1" s="49">
-      <c r="A309" s="6" t="n"/>
-      <c r="B309" s="24" t="n"/>
-      <c r="C309" s="29" t="n"/>
+      <c r="A309" s="6" t="inlineStr">
+        <is>
+          <t>P2000 | Grassland 0.370970904827</t>
+        </is>
+      </c>
+      <c r="B309" s="24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C309" s="29" t="n">
+        <v>4</v>
+      </c>
       <c r="D309" s="7">
         <f>IF(C309="","",C309*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -11031,9 +11031,17 @@
       <c r="H309" s="9" t="n"/>
     </row>
     <row r="310" ht="19.5" customHeight="1" s="49">
-      <c r="A310" s="10" t="n"/>
-      <c r="B310" s="25" t="n"/>
-      <c r="C310" s="30" t="n"/>
+      <c r="A310" s="10" t="inlineStr">
+        <is>
+          <t>AK-47 | Slate 0.990183711052</t>
+        </is>
+      </c>
+      <c r="B310" s="25" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="C310" s="30" t="n">
+        <v>7.3</v>
+      </c>
       <c r="D310" s="11">
         <f>IF(C310="","",C310*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -11061,9 +11061,17 @@
       <c r="H310" s="13" t="n"/>
     </row>
     <row r="311" ht="19.5" customHeight="1" s="49">
-      <c r="A311" s="6" t="n"/>
-      <c r="B311" s="24" t="n"/>
-      <c r="C311" s="29" t="n"/>
+      <c r="A311" s="6" t="inlineStr">
+        <is>
+          <t>Nova | Walnut 0.650051534176</t>
+        </is>
+      </c>
+      <c r="B311" s="24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C311" s="29" t="n">
+        <v>2.8</v>
+      </c>
       <c r="D311" s="7">
         <f>IF(C311="","",C311*$B$1)</f>
         <v/>

--- a/CS_GO_PnL_Tracker_Final.xlsx
+++ b/CS_GO_PnL_Tracker_Final.xlsx
@@ -11091,9 +11091,17 @@
       <c r="H311" s="9" t="n"/>
     </row>
     <row r="312" ht="19.5" customHeight="1" s="49">
-      <c r="A312" s="10" t="n"/>
-      <c r="B312" s="25" t="n"/>
-      <c r="C312" s="30" t="n"/>
+      <c r="A312" s="10" t="inlineStr">
+        <is>
+          <t>Nova | Predator 0.772752285004</t>
+        </is>
+      </c>
+      <c r="B312" s="25" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="C312" s="30" t="n">
+        <v>8.35</v>
+      </c>
       <c r="D312" s="11">
         <f>IF(C312="","",C312*$B$1)</f>
         <v/>
